--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D178"/>
+  <dimension ref="A1:D179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="31.5703125" customWidth="1" min="1" max="1"/>
@@ -3663,6 +3663,23 @@
         </is>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Stag's Leap</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>StagsLeap</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D179"/>
+  <dimension ref="A1:D180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="31.5703125" customWidth="1" min="1" max="1"/>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>Unico, Tempranillo</t>
+          <t>Unico, Tempranillo, Vega</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -3675,6 +3675,23 @@
         </is>
       </c>
       <c r="C179" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Cliff Lede Poetry</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>CliffLede</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
         <is>
           <t>standalone producer</t>
         </is>

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D180"/>
+  <dimension ref="A1:D183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="31.5703125" customWidth="1" min="1" max="1"/>
@@ -3697,6 +3697,57 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Les Carmes Haut-Brion</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>LesCarmesHB</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Macdonald</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Macdonald</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Araujo Estate</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Araujo</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D183"/>
+  <dimension ref="A1:D184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="31.5703125" customWidth="1" min="1" max="1"/>
@@ -3748,6 +3748,23 @@
         </is>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Luciano Sandrone</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Sandrone</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Maya</t>
+          <t>Maya, DallaValle</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D184"/>
+  <dimension ref="A1:D185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="31.5703125" customWidth="1" min="1" max="1"/>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Maya, DallaValle</t>
+          <t>DallaValle</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -3762,6 +3762,23 @@
       <c r="C184" t="inlineStr">
         <is>
           <t>standalone producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Dalla Valle Maya</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Maya</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
         </is>
       </c>
     </row>

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D185"/>
+  <dimension ref="A1:D186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="31.5703125" customWidth="1" min="1" max="1"/>
@@ -3782,6 +3782,23 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Bonnes-Mares</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>BonnesMares</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
